--- a/data/dividends_info_20260716.xlsx
+++ b/data/dividends_info_20260716.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>56.97000122070312</v>
+        <v>55.9900016784668</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1579778797113552</v>
+        <v>0.1607429850008615</v>
       </c>
       <c r="J2" t="n">
         <v>242</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.34999847412109</v>
+        <v>65.19999694824219</v>
       </c>
       <c r="I3" t="n">
-        <v>1.087801113595226</v>
+        <v>1.073619682153792</v>
       </c>
       <c r="J3" t="n">
         <v>221</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.300000190734863</v>
+        <v>9.380000114440918</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6451612770908873</v>
+        <v>0.6396588408098992</v>
       </c>
       <c r="J4" t="n">
         <v>151</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>56.95999908447266</v>
+        <v>55.9900016784668</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1580056205171781</v>
+        <v>0.1607429850008615</v>
       </c>
       <c r="J6" t="n">
         <v>151</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.144999980926514</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I7" t="n">
-        <v>3.589743621663835</v>
+        <v>3.564814673161806</v>
       </c>
       <c r="J7" t="n">
         <v>130</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.11499977111816</v>
+        <v>21.11000061035156</v>
       </c>
       <c r="I8" t="n">
-        <v>1.278711830105324</v>
+        <v>1.279014648003383</v>
       </c>
       <c r="J8" t="n">
         <v>130</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.110000133514404</v>
+        <v>6.139999866485596</v>
       </c>
       <c r="I9" t="n">
-        <v>3.273322350730658</v>
+        <v>3.257329061058689</v>
       </c>
       <c r="J9" t="n">
         <v>123</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.900000095367432</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8474576134203634</v>
+        <v>0.8361203986709481</v>
       </c>
       <c r="J12" t="n">
         <v>81</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.940000057220459</v>
+        <v>4.900000095367432</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7692307603207009</v>
+        <v>0.7755101889880786</v>
       </c>
       <c r="J13" t="n">
         <v>74</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.11499977111816</v>
+        <v>21.11000061035156</v>
       </c>
       <c r="I14" t="n">
-        <v>1.278711830105324</v>
+        <v>1.279014648003383</v>
       </c>
       <c r="J14" t="n">
         <v>67</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>56.95999908447266</v>
+        <v>55.9900016784668</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1580056205171781</v>
+        <v>0.1607429850008615</v>
       </c>
       <c r="J15" t="n">
         <v>67</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.820000171661377</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I16" t="n">
-        <v>5.154639023221232</v>
+        <v>5.300353499782643</v>
       </c>
       <c r="J16" t="n">
         <v>60</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.940000057220459</v>
+        <v>4.900000095367432</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7692307603207009</v>
+        <v>0.7755101889880786</v>
       </c>
       <c r="J18" t="n">
         <v>18</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.789999961853027</v>
+        <v>2.799999952316284</v>
       </c>
       <c r="I19" t="n">
-        <v>5.303548459610866</v>
+        <v>5.284607232853467</v>
       </c>
       <c r="J19" t="n">
         <v>18</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.699999809265137</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="I20" t="n">
-        <v>4.385965059044991</v>
+        <v>4.363001730677547</v>
       </c>
       <c r="J20" t="n">
         <v>11</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4.130000114440918</v>
+        <v>4.199999809265137</v>
       </c>
       <c r="I21" t="n">
-        <v>3.38983041454351</v>
+        <v>3.333333484710216</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>10.0600004196167</v>
+        <v>10.00399971008301</v>
       </c>
       <c r="I22" t="n">
-        <v>2.58449293394668</v>
+        <v>2.59896049115182</v>
       </c>
       <c r="J22" t="n">
         <v>4</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>14.07999992370605</v>
+        <v>14.22000026702881</v>
       </c>
       <c r="I23" t="n">
-        <v>4.261363659454279</v>
+        <v>4.21940920346668</v>
       </c>
       <c r="J23" t="n">
         <v>4</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.829999923706055</v>
+        <v>2.834000110626221</v>
       </c>
       <c r="I24" t="n">
-        <v>7.77385179968121</v>
+        <v>7.762879019485544</v>
       </c>
       <c r="J24" t="n">
         <v>4</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6.824999809265137</v>
+        <v>6.849999904632568</v>
       </c>
       <c r="I26" t="n">
-        <v>3.516483614756926</v>
+        <v>3.503649683815193</v>
       </c>
       <c r="J26" t="n">
         <v>4</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>19.10000038146973</v>
+        <v>19.04999923706055</v>
       </c>
       <c r="I27" t="n">
-        <v>1.968586348117482</v>
+        <v>1.973753359887365</v>
       </c>
       <c r="J27" t="n">
         <v>4</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3.019999980926514</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="I31" t="n">
-        <v>4.966887448588033</v>
+        <v>4.934210588231972</v>
       </c>
       <c r="J31" t="n">
         <v>-3</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4.550000190734863</v>
+        <v>4.5</v>
       </c>
       <c r="I33" t="n">
-        <v>1.538461473969618</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="J33" t="n">
         <v>-10</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>35.34999847412109</v>
+        <v>35.65000152587891</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4243281654165034</v>
+        <v>0.4207573452447473</v>
       </c>
       <c r="J34" t="n">
         <v>-10</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>21.79999923706055</v>
+        <v>21.63999938964844</v>
       </c>
       <c r="I37" t="n">
-        <v>1.146789030960119</v>
+        <v>1.155268054765234</v>
       </c>
       <c r="J37" t="n">
         <v>-24</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>27.64999961853027</v>
+        <v>28.04999923706055</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7052441326954534</v>
+        <v>0.6951871846839832</v>
       </c>
       <c r="J38" t="n">
         <v>-24</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3.868000030517578</v>
+        <v>3.874000072479248</v>
       </c>
       <c r="I41" t="n">
-        <v>4.136504620931722</v>
+        <v>4.130098012559009</v>
       </c>
       <c r="J41" t="n">
         <v>-24</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2.529999971389771</v>
+        <v>2.533999919891357</v>
       </c>
       <c r="I42" t="n">
-        <v>5.478260931515535</v>
+        <v>5.469613432582205</v>
       </c>
       <c r="J42" t="n">
         <v>-24</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>49.79000091552734</v>
+        <v>49.61000061035156</v>
       </c>
       <c r="I43" t="n">
-        <v>1.265314296878292</v>
+        <v>1.269905245412444</v>
       </c>
       <c r="J43" t="n">
         <v>-24</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6.235000133514404</v>
+        <v>6.28000020980835</v>
       </c>
       <c r="I44" t="n">
-        <v>2.245388885358178</v>
+        <v>2.229299288578726</v>
       </c>
       <c r="J44" t="n">
         <v>-24</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>28.04000091552734</v>
+        <v>27.70999908447266</v>
       </c>
       <c r="I46" t="n">
-        <v>3.031383638540848</v>
+        <v>3.06748476392516</v>
       </c>
       <c r="J46" t="n">
         <v>-24</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>56.95999908447266</v>
+        <v>55.9900016784668</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1580056205171781</v>
+        <v>0.1607429850008615</v>
       </c>
       <c r="J47" t="n">
         <v>-24</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>6.078000068664551</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="I49" t="n">
-        <v>2.982889074560918</v>
+        <v>2.962418356049326</v>
       </c>
       <c r="J49" t="n">
         <v>-24</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>9.520000457763672</v>
+        <v>9.630000114440918</v>
       </c>
       <c r="I50" t="n">
-        <v>2.731092305651802</v>
+        <v>2.699896125755079</v>
       </c>
       <c r="J50" t="n">
         <v>-24</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>10.0649995803833</v>
+        <v>10.0600004196167</v>
       </c>
       <c r="I51" t="n">
-        <v>2.752111391438838</v>
+        <v>2.753479010397041</v>
       </c>
       <c r="J51" t="n">
         <v>-24</v>
@@ -4487,7 +4487,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4565,14 +4565,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4582,14 +4582,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4599,14 +4599,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4616,14 +4616,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4633,14 +4633,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4650,14 +4650,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4667,14 +4667,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4691,7 +4691,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4810,7 +4810,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4820,14 +4820,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4837,14 +4837,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4854,14 +4854,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4871,14 +4871,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4888,14 +4888,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4905,14 +4905,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4922,14 +4922,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4946,7 +4946,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4963,7 +4963,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4980,7 +4980,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4997,7 +4997,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5007,14 +5007,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5031,7 +5031,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5041,14 +5041,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5065,7 +5065,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5075,14 +5075,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5116,7 +5116,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5133,7 +5133,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5143,14 +5143,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5160,14 +5160,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5184,7 +5184,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5201,7 +5201,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5218,7 +5218,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5228,14 +5228,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5252,7 +5252,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5269,7 +5269,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5279,14 +5279,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5303,7 +5303,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5320,7 +5320,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5337,7 +5337,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5347,14 +5347,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5364,14 +5364,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5388,7 +5388,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5405,7 +5405,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5415,14 +5415,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5432,14 +5432,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5456,7 +5456,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5466,14 +5466,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5483,14 +5483,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5500,14 +5500,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5524,7 +5524,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5534,14 +5534,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5551,14 +5551,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5575,7 +5575,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5592,7 +5592,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5602,14 +5602,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5660,7 +5660,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5677,7 +5677,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5711,7 +5711,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5745,7 +5745,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5762,7 +5762,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5779,7 +5779,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5806,14 +5806,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5830,7 +5830,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5840,14 +5840,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5857,14 +5857,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5881,7 +5881,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5898,7 +5898,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5915,7 +5915,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5925,14 +5925,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5949,7 +5949,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5959,14 +5959,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5983,7 +5983,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5993,14 +5993,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6010,14 +6010,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6027,14 +6027,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6061,14 +6061,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6078,14 +6078,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -6112,14 +6112,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6153,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6187,7 +6187,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6204,7 +6204,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6214,14 +6214,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6238,7 +6238,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6255,7 +6255,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6272,7 +6272,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6289,7 +6289,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6306,7 +6306,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6323,7 +6323,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6340,7 +6340,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6357,7 +6357,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6401,14 +6401,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6425,7 +6425,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6442,7 +6442,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6452,14 +6452,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6476,7 +6476,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6486,14 +6486,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6510,7 +6510,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6527,7 +6527,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6571,14 +6571,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6612,7 +6612,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6622,14 +6622,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
